--- a/etc/hebrew/quantifiers.xlsx
+++ b/etc/hebrew/quantifiers.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -542,6 +542,27 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>any; no</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>שׁוּם</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>quantifier</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/etc/hebrew/quantifiers.xlsx
+++ b/etc/hebrew/quantifiers.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -563,6 +563,27 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>lots; a lot</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>הֲמוֹן</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>quantifier</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
